--- a/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
+++ b/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3875" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3915" uniqueCount="439">
   <si>
     <t>Datum</t>
   </si>
@@ -365,6 +365,18 @@
   </si>
   <si>
     <t>10 min 57 s</t>
+  </si>
+  <si>
+    <t>16.06.2026</t>
+  </si>
+  <si>
+    <t>15 min 40 s</t>
+  </si>
+  <si>
+    <t>17.06.2026</t>
+  </si>
+  <si>
+    <t>11 min 15 s</t>
   </si>
   <si>
     <t>01.05.2026</t>
@@ -4139,6 +4151,293 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P63" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="S63" s="3">
+        <v>12044.400000000005</v>
+      </c>
+      <c r="T63" s="3">
+        <v>5535.0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>2100.0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>2871.0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>338.0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>1835.0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>1289.0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>26012.40000000001</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>-3.637978807091713E-12</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0.32477838569297707</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>922.0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM63" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>74.0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR63" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS63" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AT63" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AU63" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AV63" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P67" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S67" s="3">
+        <v>13752.000000000005</v>
+      </c>
+      <c r="T67" s="3">
+        <v>3761.0</v>
+      </c>
+      <c r="U67" s="3">
+        <v>4640.0</v>
+      </c>
+      <c r="V67" s="3">
+        <v>4830.0</v>
+      </c>
+      <c r="W67" s="3">
+        <v>609.6</v>
+      </c>
+      <c r="X67" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y67" s="3">
+        <v>2547.0</v>
+      </c>
+      <c r="AA67" s="3">
+        <v>1089.0</v>
+      </c>
+      <c r="AB67" s="3">
+        <v>31844.100000000013</v>
+      </c>
+      <c r="AC67" s="3">
+        <v>0.49999999999272404</v>
+      </c>
+      <c r="AD67" s="3">
+        <v>0.3713021175037133</v>
+      </c>
+      <c r="AH67" s="3">
+        <v>616.0</v>
+      </c>
+      <c r="AI67" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ67" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AK67" s="3">
+        <v>1411.8</v>
+      </c>
+      <c r="AL67" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM67" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AN67" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO67" s="3">
+        <v>94.0</v>
+      </c>
+      <c r="AP67" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="AQ67" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR67" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS67" s="3">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AT67" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU67" s="3">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AV67" s="3">
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4299,19 +4598,19 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>59</v>
@@ -4319,7 +4618,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>81</v>
@@ -4331,7 +4630,7 @@
         <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>59</v>
@@ -4339,7 +4638,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>81</v>
@@ -4362,7 +4661,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>81</v>
@@ -4371,7 +4670,7 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>54</v>
@@ -4422,7 +4721,7 @@
         <v>2.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AN5" s="3">
         <v>0.0</v>
@@ -4454,7 +4753,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>87</v>
@@ -4474,13 +4773,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>65</v>
@@ -4494,7 +4793,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>87</v>
@@ -4554,7 +4853,7 @@
         <v>0.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AN8" s="3">
         <v>0.0</v>
@@ -4586,13 +4885,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>51</v>
@@ -4606,7 +4905,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>92</v>
@@ -4626,13 +4925,13 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>59</v>
@@ -4641,7 +4940,7 @@
         <v>65</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M11" s="3">
         <v>3.0</v>
@@ -4655,7 +4954,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>92</v>
@@ -4664,7 +4963,7 @@
         <v>8.0</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>64</v>
@@ -4715,7 +5014,7 @@
         <v>1.0</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AN12" s="3">
         <v>1.0</v>
@@ -4747,13 +5046,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>59</v>
@@ -4767,7 +5066,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -4787,7 +5086,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -4796,7 +5095,7 @@
         <v>5.0</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>54</v>
@@ -4847,7 +5146,7 @@
         <v>1.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AN15" s="3">
         <v>0.0</v>
@@ -4879,7 +5178,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -4899,7 +5198,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>63</v>
@@ -4928,7 +5227,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>63</v>
@@ -4988,7 +5287,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -5020,13 +5319,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>51</v>
@@ -5040,7 +5339,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>69</v>
@@ -5060,7 +5359,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>69</v>
@@ -5093,7 +5392,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>69</v>
@@ -5106,7 +5405,7 @@
         <v>0.0</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>64</v>
@@ -5160,7 +5459,7 @@
         <v>1.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -5192,7 +5491,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>78</v>
@@ -5212,7 +5511,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>78</v>
@@ -5232,7 +5531,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>78</v>
@@ -5261,7 +5560,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>78</v>
@@ -5324,7 +5623,7 @@
         <v>0.0</v>
       </c>
       <c r="AM26" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AN26" s="3">
         <v>1.0</v>
@@ -5356,7 +5655,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>81</v>
@@ -5376,7 +5675,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>81</v>
@@ -5396,7 +5695,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>81</v>
@@ -5429,7 +5728,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>81</v>
@@ -5499,7 +5798,7 @@
         <v>0.0</v>
       </c>
       <c r="AM30" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AN30" s="3">
         <v>1.0</v>
@@ -5531,13 +5830,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>51</v>
@@ -5551,7 +5850,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>87</v>
@@ -5571,13 +5870,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>65</v>
@@ -5591,13 +5890,13 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>51</v>
@@ -5620,7 +5919,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>87</v>
@@ -5629,7 +5928,7 @@
         <v>7.0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>54</v>
@@ -5683,7 +5982,7 @@
         <v>1.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="AN35" s="3">
         <v>1.0</v>
@@ -5715,13 +6014,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>51</v>
@@ -5735,7 +6034,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>92</v>
@@ -5755,13 +6054,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>59</v>
@@ -5770,7 +6069,7 @@
         <v>65</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M38" s="3">
         <v>2.0</v>
@@ -5784,7 +6083,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>92</v>
@@ -5793,7 +6092,7 @@
         <v>9.0</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>54</v>
@@ -5847,7 +6146,7 @@
         <v>0.0</v>
       </c>
       <c r="AM39" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AN39" s="3">
         <v>1.0</v>
@@ -5879,7 +6178,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
@@ -5899,13 +6198,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>65</v>
@@ -5914,12 +6213,12 @@
         <v>73</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>49</v>
@@ -5931,7 +6230,7 @@
         <v>64</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="S42" s="3">
         <v>11900.0</v>
@@ -6011,7 +6310,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>63</v>
@@ -6031,7 +6330,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>63</v>
@@ -6060,7 +6359,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>63</v>
@@ -6120,7 +6419,7 @@
         <v>5.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AN45" s="3">
         <v>1.0</v>
@@ -6152,7 +6451,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>69</v>
@@ -6172,7 +6471,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>69</v>
@@ -6192,7 +6491,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>69</v>
@@ -6221,7 +6520,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>69</v>
@@ -6281,7 +6580,7 @@
         <v>1.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -6313,13 +6612,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>51</v>
@@ -6333,7 +6632,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>78</v>
@@ -6362,7 +6661,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>78</v>
@@ -6371,10 +6670,10 @@
         <v>0.0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="S52" s="3">
         <v>9727.0</v>
@@ -6422,7 +6721,7 @@
         <v>1.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -6454,7 +6753,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>81</v>
@@ -6466,7 +6765,7 @@
         <v>51</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>51</v>
@@ -6474,16 +6773,16 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>83</v>
@@ -6494,13 +6793,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>65</v>
@@ -6514,7 +6813,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>81</v>
@@ -6543,7 +6842,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>81</v>
@@ -6555,7 +6854,7 @@
         <v>64</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="S57" s="3">
         <v>21791.6</v>
@@ -6603,7 +6902,7 @@
         <v>0.0</v>
       </c>
       <c r="AM57" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AN57" s="3">
         <v>1.0</v>
@@ -6635,7 +6934,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>87</v>
@@ -6655,13 +6954,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>55</v>
@@ -6678,7 +6977,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>87</v>
@@ -6738,7 +7037,7 @@
         <v>7.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AN60" s="3">
         <v>0.0</v>
@@ -6770,7 +7069,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>92</v>
@@ -6790,13 +7089,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>51</v>
@@ -6810,7 +7109,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>92</v>
@@ -6871,7 +7170,7 @@
         <v>2.0</v>
       </c>
       <c r="AM63" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AN63" s="3">
         <v>0.0</v>
@@ -6903,7 +7202,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -6923,7 +7222,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -7015,13 +7314,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>51</v>
@@ -7035,7 +7334,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>63</v>
@@ -7055,7 +7354,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>63</v>
@@ -7084,7 +7383,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>63</v>
@@ -7093,7 +7392,7 @@
         <v>2.0</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>54</v>
@@ -7147,7 +7446,7 @@
         <v>2.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AN69" s="3">
         <v>1.0</v>
@@ -7179,7 +7478,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
@@ -7199,7 +7498,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>69</v>
@@ -7228,7 +7527,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>69</v>
@@ -7320,7 +7619,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>78</v>
@@ -7340,7 +7639,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>78</v>
@@ -7360,7 +7659,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>78</v>
@@ -7380,7 +7679,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>78</v>
@@ -7409,7 +7708,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>78</v>
@@ -7469,7 +7768,7 @@
         <v>1.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AN77" s="3">
         <v>1.0</v>
@@ -7501,7 +7800,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>81</v>
@@ -7521,7 +7820,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>81</v>
@@ -7550,7 +7849,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>81</v>
@@ -7613,7 +7912,7 @@
         <v>1.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AN80" s="3">
         <v>1.0</v>
@@ -7645,7 +7944,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>87</v>
@@ -7654,24 +7953,24 @@
         <v>54</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>51</v>
@@ -7685,7 +7984,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>87</v>
@@ -7714,7 +8013,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>87</v>
@@ -7723,7 +8022,7 @@
         <v>2.0</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="R84" s="1" t="s">
         <v>54</v>
@@ -7806,7 +8105,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>92</v>
@@ -7826,7 +8125,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>92</v>
@@ -7846,7 +8145,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>92</v>
@@ -7875,7 +8174,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>92</v>
@@ -7935,7 +8234,7 @@
         <v>3.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -7967,7 +8266,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -7987,7 +8286,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -8016,7 +8315,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -8079,7 +8378,7 @@
         <v>4.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -8111,7 +8410,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>63</v>
@@ -8131,7 +8430,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>63</v>
@@ -8151,7 +8450,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>63</v>
@@ -8171,7 +8470,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>63</v>
@@ -8234,7 +8533,7 @@
         <v>1.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AN95" s="3">
         <v>0.0</v>
@@ -8266,7 +8565,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
@@ -8286,7 +8585,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -8306,7 +8605,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>69</v>
@@ -8335,7 +8634,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>69</v>
@@ -8395,7 +8694,7 @@
         <v>2.0</v>
       </c>
       <c r="AM99" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AN99" s="3">
         <v>1.0</v>
@@ -8427,7 +8726,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>78</v>
@@ -8447,7 +8746,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>78</v>
@@ -8467,7 +8766,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>78</v>
@@ -8487,7 +8786,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>78</v>
@@ -8516,7 +8815,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>78</v>
@@ -8579,7 +8878,7 @@
         <v>1.0</v>
       </c>
       <c r="AM104" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AN104" s="3">
         <v>1.0</v>
@@ -8611,7 +8910,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>81</v>
@@ -8631,7 +8930,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>81</v>
@@ -8651,7 +8950,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>81</v>
@@ -8671,7 +8970,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>81</v>
@@ -8700,7 +8999,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>81</v>
@@ -8760,7 +9059,7 @@
         <v>1.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -8792,7 +9091,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>87</v>
@@ -8812,7 +9111,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>87</v>
@@ -8821,7 +9120,7 @@
         <v>54</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>83</v>
@@ -8832,7 +9131,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>87</v>
@@ -8861,7 +9160,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>87</v>
@@ -8924,7 +9223,7 @@
         <v>0.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AN113" s="3">
         <v>1.0</v>
@@ -8956,7 +9255,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>92</v>
@@ -8976,7 +9275,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>92</v>
@@ -8991,12 +9290,12 @@
         <v>84</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>92</v>
@@ -9016,7 +9315,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>92</v>
@@ -9045,7 +9344,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>92</v>
@@ -9105,7 +9404,7 @@
         <v>3.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -9295,13 +9594,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -9315,7 +9614,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
@@ -9335,7 +9634,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
@@ -9364,7 +9663,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>69</v>
@@ -9373,7 +9672,7 @@
         <v>2.0</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>54</v>
@@ -9430,7 +9729,7 @@
         <v>1.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -9462,7 +9761,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>78</v>
@@ -9482,7 +9781,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>78</v>
@@ -9511,7 +9810,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>78</v>
@@ -9574,7 +9873,7 @@
         <v>0.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AN8" s="3">
         <v>1.0</v>
@@ -9606,7 +9905,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>81</v>
@@ -9626,7 +9925,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>81</v>
@@ -9636,7 +9935,7 @@
       <c r="E10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>104</v>
@@ -9653,7 +9952,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>81</v>
@@ -9720,7 +10019,7 @@
         <v>3.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
@@ -9752,7 +10051,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>87</v>
@@ -9772,13 +10071,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>59</v>
@@ -9801,7 +10100,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>87</v>
@@ -9864,7 +10163,7 @@
         <v>2.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -9896,7 +10195,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>92</v>
@@ -9916,13 +10215,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>59</v>
@@ -9945,7 +10244,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>92</v>
@@ -10005,7 +10304,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN17" s="3">
         <v>1.0</v>
@@ -10037,7 +10336,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>49</v>
@@ -10057,7 +10356,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
@@ -10077,7 +10376,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
@@ -10106,7 +10405,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
@@ -10169,7 +10468,7 @@
         <v>3.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -10201,13 +10500,13 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>51</v>
@@ -10221,7 +10520,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>63</v>
@@ -10241,7 +10540,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>63</v>
@@ -10270,7 +10569,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>63</v>
@@ -10279,7 +10578,7 @@
         <v>0.0</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>64</v>
@@ -10333,7 +10632,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -10365,13 +10664,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>51</v>
@@ -10385,7 +10684,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>69</v>
@@ -10405,7 +10704,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>69</v>
@@ -10434,7 +10733,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>69</v>
@@ -10443,7 +10742,7 @@
         <v>1.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>54</v>
@@ -10494,7 +10793,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -10526,7 +10825,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>78</v>
@@ -10546,7 +10845,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>78</v>
@@ -10566,7 +10865,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>78</v>
@@ -10595,7 +10894,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>78</v>
@@ -10655,7 +10954,7 @@
         <v>2.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -10687,7 +10986,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>81</v>
@@ -10707,13 +11006,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>71</v>
@@ -10722,12 +11021,12 @@
         <v>52</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>81</v>
@@ -10756,7 +11055,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>81</v>
@@ -10819,7 +11118,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -10851,33 +11150,33 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>65</v>
@@ -10886,24 +11185,24 @@
         <v>88</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>82</v>
@@ -10911,7 +11210,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>87</v>
@@ -10924,10 +11223,10 @@
         <v>9.0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="S41" s="3">
         <v>17084.0</v>
@@ -10975,7 +11274,7 @@
         <v>2.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AN41" s="3">
         <v>0.0</v>
@@ -11007,13 +11306,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -11027,7 +11326,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>92</v>
@@ -11047,7 +11346,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>92</v>
@@ -11067,7 +11366,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>92</v>
@@ -11077,7 +11376,7 @@
       <c r="E45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>65</v>
@@ -11094,7 +11393,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>92</v>
@@ -11107,7 +11406,7 @@
         <v>2.0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>54</v>
@@ -11164,7 +11463,7 @@
         <v>1.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN46" s="3">
         <v>0.0</v>
@@ -11196,13 +11495,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>51</v>
@@ -11216,7 +11515,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
@@ -11236,7 +11535,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
@@ -11265,7 +11564,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
@@ -11274,7 +11573,7 @@
         <v>2.0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>54</v>
@@ -11325,7 +11624,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -11357,13 +11656,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>51</v>
@@ -11377,7 +11676,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>63</v>
@@ -11397,7 +11696,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>63</v>
@@ -11426,7 +11725,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>63</v>
@@ -11435,7 +11734,7 @@
         <v>1.0</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R54" s="1" t="s">
         <v>54</v>
@@ -11495,7 +11794,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -11527,19 +11826,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>74</v>
@@ -11547,7 +11846,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>69</v>
@@ -11567,7 +11866,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>69</v>
@@ -11579,10 +11878,10 @@
         <v>51</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="M57" s="3">
         <v>1.0</v>
@@ -11596,22 +11895,22 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M58" s="3">
         <v>3.0</v>
@@ -11625,7 +11924,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -11634,7 +11933,7 @@
         <v>0.0</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>54</v>
@@ -11685,7 +11984,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN59" s="3">
         <v>2.0</v>
@@ -11717,7 +12016,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>78</v>
@@ -11737,7 +12036,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>78</v>
@@ -11766,7 +12065,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>78</v>
@@ -11826,7 +12125,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -11858,7 +12157,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>81</v>
@@ -11878,7 +12177,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>81</v>
@@ -11898,7 +12197,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>81</v>
@@ -11908,7 +12207,7 @@
       <c r="E65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>59</v>
@@ -11917,7 +12216,7 @@
         <v>65</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M65" s="3">
         <v>3.0</v>
@@ -11931,7 +12230,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>81</v>
@@ -11998,7 +12297,7 @@
         <v>0.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -12030,13 +12329,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>51</v>
@@ -12050,7 +12349,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>87</v>
@@ -12070,7 +12369,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>87</v>
@@ -12085,18 +12384,18 @@
         <v>88</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>59</v>
@@ -12105,7 +12404,7 @@
         <v>65</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M70" s="3">
         <v>6.0</v>
@@ -12119,7 +12418,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>87</v>
@@ -12128,7 +12427,7 @@
         <v>8.0</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>54</v>
@@ -12179,7 +12478,7 @@
         <v>2.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -12211,7 +12510,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>92</v>
@@ -12231,7 +12530,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>92</v>
@@ -12251,7 +12550,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>92</v>
@@ -12314,7 +12613,7 @@
         <v>2.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN74" s="3">
         <v>0.0</v>
@@ -12346,19 +12645,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>74</v>
@@ -12366,7 +12665,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
@@ -12386,7 +12685,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -12415,7 +12714,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>49</v>
@@ -12424,7 +12723,7 @@
         <v>0.0</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>54</v>
@@ -12478,7 +12777,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AN78" s="3">
         <v>1.0</v>
@@ -12510,7 +12809,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>63</v>
@@ -12530,7 +12829,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>63</v>
@@ -12559,7 +12858,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>63</v>
@@ -12622,7 +12921,7 @@
         <v>1.0</v>
       </c>
       <c r="AM81" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AN81" s="3">
         <v>1.0</v>
@@ -12654,13 +12953,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>51</v>
@@ -12674,7 +12973,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>69</v>
@@ -12694,7 +12993,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>69</v>
@@ -12709,7 +13008,7 @@
         <v>109</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M84" s="3">
         <v>1.0</v>
@@ -12723,7 +13022,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>69</v>
@@ -12732,7 +13031,7 @@
         <v>8.0</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>64</v>
@@ -12783,7 +13082,7 @@
         <v>1.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AN85" s="3">
         <v>1.0</v>
@@ -12815,7 +13114,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>78</v>
@@ -12835,7 +13134,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>78</v>
@@ -12864,7 +13163,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>78</v>
@@ -12924,7 +13223,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -12956,7 +13255,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>81</v>
@@ -12976,13 +13275,13 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>59</v>
@@ -12991,7 +13290,7 @@
         <v>65</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M90" s="3">
         <v>6.0</v>
@@ -13005,7 +13304,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>81</v>
@@ -13065,7 +13364,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -13097,7 +13396,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>87</v>
@@ -13117,13 +13416,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>59</v>
@@ -13132,7 +13431,7 @@
         <v>65</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M93" s="3">
         <v>4.0</v>
@@ -13146,13 +13445,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>65</v>
@@ -13175,7 +13474,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>87</v>
@@ -13235,7 +13534,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AN95" s="3">
         <v>2.0</v>
@@ -13267,7 +13566,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>92</v>
@@ -13287,7 +13586,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>92</v>
@@ -13347,7 +13646,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -13379,7 +13678,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -13399,7 +13698,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -13414,7 +13713,7 @@
         <v>109</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N99" s="1" t="b">
         <v>1</v>
@@ -13422,7 +13721,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -13482,7 +13781,7 @@
         <v>0.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AN100" s="3">
         <v>0.0</v>
@@ -13514,7 +13813,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>63</v>
@@ -13534,7 +13833,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>63</v>
@@ -13554,7 +13853,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>63</v>
@@ -13614,7 +13913,7 @@
         <v>1.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AN103" s="3">
         <v>0.0</v>
@@ -13646,7 +13945,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>69</v>
@@ -13666,7 +13965,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>69</v>
@@ -13675,13 +13974,13 @@
         <v>58</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M105" s="3">
         <v>8.0</v>
@@ -13689,7 +13988,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>69</v>
@@ -13755,7 +14054,7 @@
         <v>2.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AN106" s="3">
         <v>0.0</v>
@@ -13787,7 +14086,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>78</v>
@@ -13807,7 +14106,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>78</v>
@@ -13822,7 +14121,7 @@
         <v>73</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M108" s="3">
         <v>9.0</v>
@@ -13830,7 +14129,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>78</v>
@@ -13890,7 +14189,7 @@
         <v>2.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AN109" s="3">
         <v>0.0</v>
@@ -14080,7 +14379,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>92</v>
@@ -14100,7 +14399,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>92</v>
@@ -14120,13 +14419,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>59</v>
@@ -14149,7 +14448,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>92</v>
@@ -14212,7 +14511,7 @@
         <v>5.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -14244,7 +14543,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>49</v>
@@ -14264,7 +14563,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>49</v>
@@ -14284,13 +14583,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>51</v>
@@ -14304,7 +14603,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -14333,7 +14632,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -14393,7 +14692,7 @@
         <v>0.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AN10" s="3">
         <v>1.0</v>
@@ -14425,7 +14724,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>63</v>
@@ -14445,13 +14744,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>59</v>
@@ -14474,7 +14773,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>63</v>
@@ -14537,7 +14836,7 @@
         <v>3.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AN13" s="3">
         <v>1.0</v>
@@ -14569,7 +14868,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>69</v>
@@ -14589,13 +14888,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -14609,7 +14908,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
@@ -14629,7 +14928,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
@@ -14652,7 +14951,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>69</v>
@@ -14715,7 +15014,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AN18" s="3">
         <v>0.0</v>
@@ -14747,7 +15046,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>78</v>
@@ -14767,7 +15066,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>78</v>
@@ -14787,7 +15086,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>78</v>
@@ -14810,7 +15109,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>78</v>
@@ -14876,7 +15175,7 @@
         <v>2.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AN22" s="3">
         <v>0.0</v>
@@ -14908,7 +15207,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>81</v>
@@ -14928,7 +15227,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>81</v>
@@ -14938,7 +15237,7 @@
       <c r="E24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>51</v>
@@ -14961,7 +15260,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>81</v>
@@ -15025,7 +15324,7 @@
         <v>3.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -15057,13 +15356,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>51</v>
@@ -15077,13 +15376,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>109</v>
@@ -15097,7 +15396,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>87</v>
@@ -15107,7 +15406,7 @@
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>59</v>
@@ -15130,7 +15429,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>87</v>
@@ -15143,10 +15442,10 @@
         <v>5.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="S29" s="3">
         <v>13413.0</v>
@@ -15194,7 +15493,7 @@
         <v>7.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -15226,13 +15525,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>51</v>
@@ -15241,12 +15540,12 @@
         <v>55</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>92</v>
@@ -15256,7 +15555,7 @@
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>59</v>
@@ -15279,7 +15578,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>92</v>
@@ -15292,10 +15591,10 @@
         <v>3.0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="S32" s="3">
         <v>12040.0</v>
@@ -15346,7 +15645,7 @@
         <v>9.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AN32" s="3">
         <v>1.0</v>
@@ -15378,7 +15677,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
@@ -15398,7 +15697,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -15427,7 +15726,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
@@ -15487,7 +15786,7 @@
         <v>0.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AN35" s="3">
         <v>1.0</v>
@@ -15519,7 +15818,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>63</v>
@@ -15539,7 +15838,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>63</v>
@@ -15568,7 +15867,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>63</v>
@@ -15628,7 +15927,7 @@
         <v>0.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AN38" s="3">
         <v>1.0</v>
@@ -15660,13 +15959,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>51</v>
@@ -15680,7 +15979,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>69</v>
@@ -15700,33 +15999,33 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>51</v>
@@ -15740,7 +16039,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
@@ -15769,7 +16068,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
@@ -15778,7 +16077,7 @@
         <v>0.0</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>54</v>
@@ -15829,7 +16128,7 @@
         <v>1.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -15861,13 +16160,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>51</v>
@@ -15881,7 +16180,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>78</v>
@@ -15901,27 +16200,27 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>78</v>
@@ -15931,7 +16230,7 @@
       <c r="E48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>59</v>
@@ -15940,12 +16239,12 @@
         <v>65</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>78</v>
@@ -15978,7 +16277,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>78</v>
@@ -15991,7 +16290,7 @@
         <v>0.0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>54</v>
@@ -16045,7 +16344,7 @@
         <v>1.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -16077,7 +16376,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>81</v>
@@ -16089,7 +16388,7 @@
         <v>51</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>93</v>
@@ -16097,7 +16396,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>81</v>
@@ -16117,13 +16416,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>59</v>
@@ -16140,7 +16439,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>81</v>
@@ -16203,7 +16502,7 @@
         <v>3.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AN54" s="3">
         <v>0.0</v>
@@ -16235,7 +16534,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>87</v>
@@ -16255,7 +16554,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>87</v>
@@ -16267,30 +16566,30 @@
         <v>65</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>59</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="M57" s="3">
         <v>13.0</v>
@@ -16298,7 +16597,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>87</v>
@@ -16361,7 +16660,7 @@
         <v>5.0</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AN58" s="3">
         <v>0.0</v>
@@ -16393,7 +16692,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>92</v>
@@ -16413,13 +16712,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>59</v>
@@ -16436,7 +16735,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>92</v>
@@ -16496,7 +16795,7 @@
         <v>6.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN61" s="3">
         <v>0.0</v>
@@ -16528,13 +16827,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>51</v>
@@ -16548,7 +16847,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -16568,7 +16867,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -16580,7 +16879,7 @@
         <v>59</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>53</v>
@@ -16597,7 +16896,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -16606,7 +16905,7 @@
         <v>1.0</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R65" s="1" t="s">
         <v>54</v>
@@ -16657,7 +16956,7 @@
         <v>2.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -16689,7 +16988,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>63</v>
@@ -16709,7 +17008,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>63</v>
@@ -16738,7 +17037,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>63</v>
@@ -16798,7 +17097,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -16830,7 +17129,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>69</v>
@@ -16850,7 +17149,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
@@ -16879,7 +17178,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>69</v>
@@ -16939,7 +17238,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -16971,13 +17270,13 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>51</v>
@@ -16991,7 +17290,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>78</v>
@@ -17011,13 +17310,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>71</v>
@@ -17026,12 +17325,12 @@
         <v>52</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>78</v>
@@ -17060,7 +17359,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>78</v>
@@ -17069,7 +17368,7 @@
         <v>2.0</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>54</v>
@@ -17123,7 +17422,7 @@
         <v>0.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -17155,7 +17454,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>81</v>
@@ -17175,7 +17474,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>81</v>
@@ -17195,7 +17494,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>81</v>
@@ -17255,7 +17554,7 @@
         <v>4.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AN79" s="3">
         <v>0.0</v>
@@ -17287,19 +17586,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>74</v>
@@ -17307,7 +17606,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>87</v>
@@ -17327,7 +17626,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>87</v>
@@ -17339,15 +17638,15 @@
         <v>55</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>87</v>
@@ -17356,7 +17655,7 @@
         <v>15.0</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R83" s="1" t="s">
         <v>54</v>
@@ -17407,7 +17706,7 @@
         <v>5.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -17439,7 +17738,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>92</v>
@@ -17459,7 +17758,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>92</v>
@@ -17519,7 +17818,7 @@
         <v>2.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AN85" s="3">
         <v>0.0</v>
@@ -17551,7 +17850,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
@@ -17571,7 +17870,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -17591,7 +17890,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -17620,7 +17919,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -17680,7 +17979,7 @@
         <v>0.0</v>
       </c>
       <c r="AM89" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AN89" s="3">
         <v>1.0</v>
@@ -17712,19 +18011,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>74</v>
@@ -17732,7 +18031,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>63</v>
@@ -17752,7 +18051,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>63</v>
@@ -17781,7 +18080,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>63</v>
@@ -17790,7 +18089,7 @@
         <v>2.0</v>
       </c>
       <c r="Q93" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R93" s="1" t="s">
         <v>54</v>
@@ -17844,7 +18143,7 @@
         <v>0.0</v>
       </c>
       <c r="AM93" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AN93" s="3">
         <v>1.0</v>
@@ -17876,19 +18175,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>74</v>
@@ -17896,7 +18195,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>69</v>
@@ -17916,7 +18215,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
@@ -17945,7 +18244,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -17954,7 +18253,7 @@
         <v>2.0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R97" s="1" t="s">
         <v>54</v>
@@ -18040,7 +18339,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>78</v>
@@ -18060,7 +18359,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>78</v>
@@ -18089,7 +18388,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>78</v>
@@ -18152,7 +18451,7 @@
         <v>2.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AN100" s="3">
         <v>1.0</v>
@@ -18184,7 +18483,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>81</v>
@@ -18204,13 +18503,13 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>104</v>
@@ -18224,7 +18523,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>81</v>
@@ -18284,7 +18583,7 @@
         <v>4.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AN103" s="3">
         <v>0.0</v>
@@ -18316,27 +18615,27 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>87</v>
@@ -18356,33 +18655,33 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>53</v>
@@ -18405,13 +18704,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>59</v>
@@ -18420,7 +18719,7 @@
         <v>65</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N108" s="1" t="b">
         <v>1</v>
@@ -18428,7 +18727,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>87</v>
@@ -18437,7 +18736,7 @@
         <v>1.0</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>54</v>
@@ -18491,7 +18790,7 @@
         <v>1.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -18523,7 +18822,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>92</v>
@@ -18543,7 +18842,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>92</v>
@@ -18563,7 +18862,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>92</v>
@@ -18583,7 +18882,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>92</v>
@@ -18647,7 +18946,7 @@
         <v>3.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AN113" s="3">
         <v>0.0</v>
@@ -18679,7 +18978,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -18699,7 +18998,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
@@ -18719,13 +19018,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>65</v>
@@ -18739,7 +19038,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
@@ -18768,7 +19067,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -18831,7 +19130,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -18863,13 +19162,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>51</v>
@@ -18883,7 +19182,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>63</v>
@@ -18903,13 +19202,13 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>51</v>
@@ -18926,7 +19225,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>63</v>
@@ -18955,7 +19254,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>63</v>
@@ -18964,7 +19263,7 @@
         <v>0.0</v>
       </c>
       <c r="Q123" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R123" s="1" t="s">
         <v>54</v>
@@ -19021,7 +19320,7 @@
         <v>0.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -19211,13 +19510,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -19231,13 +19530,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>59</v>
@@ -19260,7 +19559,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>92</v>
@@ -19314,7 +19613,7 @@
         <v>0.0</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AN4" s="3">
         <v>1.0</v>
@@ -19346,7 +19645,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>49</v>
@@ -19366,7 +19665,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>49</v>
@@ -19395,7 +19694,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>49</v>
@@ -19455,7 +19754,7 @@
         <v>1.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN7" s="3">
         <v>1.0</v>
@@ -19487,7 +19786,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>63</v>
@@ -19507,13 +19806,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>59</v>
@@ -19536,13 +19835,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>51</v>
@@ -19559,7 +19858,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>63</v>
@@ -19616,7 +19915,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -19648,13 +19947,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>51</v>
@@ -19668,13 +19967,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>59</v>
@@ -19697,7 +19996,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>69</v>
@@ -19706,10 +20005,10 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S14" s="3">
         <v>15925.179999999997</v>
@@ -19757,7 +20056,7 @@
         <v>0.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -19789,7 +20088,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>78</v>
@@ -19809,13 +20108,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>51</v>
@@ -19832,7 +20131,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>78</v>
@@ -19861,7 +20160,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>78</v>
@@ -19918,7 +20217,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -19950,13 +20249,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>51</v>
@@ -19970,7 +20269,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>81</v>
@@ -19990,7 +20289,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>81</v>
@@ -20019,7 +20318,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>81</v>
@@ -20073,7 +20372,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -20105,13 +20404,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>51</v>
@@ -20125,19 +20424,19 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>59</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>53</v>
@@ -20154,13 +20453,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>65</v>
@@ -20177,13 +20476,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>59</v>
@@ -20206,7 +20505,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>87</v>
@@ -20260,7 +20559,7 @@
         <v>1.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AN27" s="3">
         <v>2.0</v>
@@ -20292,13 +20591,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>51</v>
@@ -20312,13 +20611,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>109</v>
@@ -20341,13 +20640,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>59</v>
@@ -20356,7 +20655,7 @@
         <v>109</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M30" s="3">
         <v>1.0</v>
@@ -20370,13 +20669,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>109</v>
@@ -20399,7 +20698,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>92</v>
@@ -20408,10 +20707,10 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S32" s="3">
         <v>9567.0</v>
@@ -20459,7 +20758,7 @@
         <v>0.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AN32" s="3">
         <v>3.0</v>
@@ -20491,13 +20790,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>51</v>
@@ -20511,7 +20810,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -20531,13 +20830,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>59</v>
@@ -20546,7 +20845,7 @@
         <v>65</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M35" s="3">
         <v>1.0</v>
@@ -20560,13 +20859,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>109</v>
@@ -20589,7 +20888,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -20598,7 +20897,7 @@
         <v>1.0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>64</v>
@@ -20649,7 +20948,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AN37" s="3">
         <v>2.0</v>
@@ -20681,13 +20980,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
@@ -20701,13 +21000,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>59</v>
@@ -20716,7 +21015,7 @@
         <v>65</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M39" s="3">
         <v>2.0</v>
@@ -20730,13 +21029,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>65</v>
@@ -20759,7 +21058,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>63</v>
@@ -20768,10 +21067,10 @@
         <v>0.0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S41" s="3">
         <v>6459.0</v>
@@ -20819,7 +21118,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -20851,7 +21150,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
@@ -20871,7 +21170,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
@@ -20900,7 +21199,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
@@ -20960,7 +21259,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -20992,7 +21291,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>78</v>
@@ -21012,13 +21311,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>51</v>
@@ -21035,7 +21334,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>78</v>
@@ -21064,7 +21363,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>78</v>
@@ -21124,7 +21423,7 @@
         <v>1.0</v>
       </c>
       <c r="AM48" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AN48" s="3">
         <v>1.0</v>
@@ -21156,13 +21455,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>51</v>
@@ -21176,7 +21475,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>81</v>
@@ -21196,7 +21495,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>81</v>
@@ -21225,7 +21524,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>81</v>
@@ -21234,10 +21533,10 @@
         <v>1.0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S52" s="3">
         <v>23294.0</v>
@@ -21282,7 +21581,7 @@
         <v>4.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -21314,13 +21613,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>75</v>
@@ -21334,7 +21633,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>87</v>
@@ -21354,13 +21653,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>59</v>
@@ -21383,7 +21682,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>87</v>
@@ -21437,7 +21736,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -21469,7 +21768,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>92</v>
@@ -21489,7 +21788,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>92</v>
@@ -21509,7 +21808,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>92</v>
@@ -21572,7 +21871,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AN59" s="3">
         <v>0.0</v>
@@ -21604,13 +21903,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>51</v>
@@ -21627,7 +21926,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -21656,7 +21955,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
@@ -21710,7 +22009,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -21742,7 +22041,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>63</v>
@@ -21762,13 +22061,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>51</v>
@@ -21785,7 +22084,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>63</v>
@@ -21814,7 +22113,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>63</v>
@@ -21871,7 +22170,7 @@
         <v>1.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -21903,7 +22202,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>69</v>
@@ -21923,7 +22222,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>69</v>
@@ -21952,7 +22251,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>69</v>
@@ -22012,7 +22311,7 @@
         <v>0.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN69" s="3">
         <v>1.0</v>
@@ -22044,7 +22343,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>78</v>
@@ -22064,7 +22363,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>78</v>
@@ -22093,7 +22392,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>78</v>
@@ -22153,7 +22452,7 @@
         <v>0.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AN72" s="3">
         <v>1.0</v>
@@ -22185,7 +22484,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>81</v>
@@ -22205,7 +22504,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>81</v>
@@ -22225,7 +22524,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>81</v>
@@ -22240,7 +22539,7 @@
         <v>109</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M75" s="3">
         <v>5.0</v>
@@ -22254,13 +22553,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>51</v>
@@ -22283,7 +22582,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>81</v>
@@ -22340,7 +22639,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AN77" s="3">
         <v>2.0</v>
@@ -22372,7 +22671,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>87</v>
@@ -22387,18 +22686,18 @@
         <v>88</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>51</v>
@@ -22415,7 +22714,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>87</v>
@@ -22472,7 +22771,7 @@
         <v>3.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AN80" s="3">
         <v>0.0</v>
@@ -22504,7 +22803,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>92</v>
@@ -22524,13 +22823,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>59</v>
@@ -22539,7 +22838,7 @@
         <v>65</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M82" s="3">
         <v>5.0</v>
@@ -22547,7 +22846,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>92</v>
@@ -22607,7 +22906,7 @@
         <v>3.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -22639,7 +22938,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>49</v>
@@ -22659,7 +22958,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>49</v>
@@ -22682,13 +22981,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>59</v>
@@ -22697,18 +22996,18 @@
         <v>65</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>71</v>
@@ -22717,12 +23016,12 @@
         <v>84</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -22782,7 +23081,7 @@
         <v>2.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AN88" s="3">
         <v>0.0</v>
@@ -22814,7 +23113,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>63</v>
@@ -22834,7 +23133,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>63</v>
@@ -22857,7 +23156,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>63</v>
@@ -22920,7 +23219,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AN91" s="3">
         <v>0.0</v>
@@ -22952,7 +23251,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>69</v>
@@ -22972,7 +23271,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>69</v>
@@ -22995,7 +23294,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>69</v>
@@ -23055,7 +23354,7 @@
         <v>0.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AN94" s="3">
         <v>0.0</v>
@@ -23087,7 +23386,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>78</v>
@@ -23107,7 +23406,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>78</v>
@@ -23130,7 +23429,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>78</v>
@@ -23190,7 +23489,7 @@
         <v>3.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -23222,13 +23521,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>51</v>
@@ -23242,7 +23541,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>81</v>
@@ -23262,7 +23561,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>81</v>
@@ -23282,13 +23581,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>65</v>
@@ -23311,7 +23610,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>81</v>
@@ -23320,7 +23619,7 @@
         <v>2.0</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>64</v>
@@ -23371,7 +23670,7 @@
         <v>0.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -23403,7 +23702,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>87</v>
@@ -23415,7 +23714,7 @@
         <v>59</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>73</v>
@@ -23423,7 +23722,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>87</v>
@@ -23432,24 +23731,24 @@
         <v>54</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>59</v>
@@ -23472,7 +23771,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>87</v>
@@ -23532,7 +23831,7 @@
         <v>1.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -23722,13 +24021,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -23742,13 +24041,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>59</v>
@@ -23762,7 +24061,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>78</v>
@@ -23782,13 +24081,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>59</v>
@@ -23811,7 +24110,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>78</v>
@@ -23840,7 +24139,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>78</v>
@@ -23894,7 +24193,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -23926,7 +24225,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>81</v>
@@ -23946,13 +24245,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>65</v>
@@ -23966,7 +24265,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>81</v>
@@ -23995,7 +24294,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>81</v>
@@ -24007,7 +24306,7 @@
         <v>64</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S11" s="3">
         <v>14680.0</v>
@@ -24055,7 +24354,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -24087,7 +24386,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>87</v>
@@ -24107,13 +24406,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>65</v>
@@ -24122,18 +24421,18 @@
         <v>88</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>59</v>
@@ -24156,7 +24455,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>87</v>
@@ -24168,7 +24467,7 @@
         <v>64</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S15" s="3">
         <v>13889.0</v>
@@ -24216,7 +24515,7 @@
         <v>0.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AN15" s="3">
         <v>1.0</v>
@@ -24248,13 +24547,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>51</v>
@@ -24268,13 +24567,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>59</v>
@@ -24297,13 +24596,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>55</v>
@@ -24317,7 +24616,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>92</v>
@@ -24371,7 +24670,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AN19" s="3">
         <v>1.0</v>
@@ -24403,7 +24702,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
@@ -24423,13 +24722,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>59</v>
@@ -24452,7 +24751,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>49</v>
@@ -24512,7 +24811,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -24544,7 +24843,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>63</v>
@@ -24564,13 +24863,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>59</v>
@@ -24593,7 +24892,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>63</v>
@@ -24653,7 +24952,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -24685,13 +24984,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>59</v>
@@ -24705,13 +25004,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>51</v>
@@ -24725,7 +25024,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>69</v>
@@ -24754,7 +25053,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>69</v>
@@ -24763,10 +25062,10 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S29" s="3">
         <v>9627.0</v>
@@ -24814,7 +25113,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -24846,13 +25145,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>51</v>
@@ -24866,7 +25165,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>78</v>
@@ -24895,13 +25194,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>51</v>
@@ -24915,7 +25214,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>78</v>
@@ -24924,10 +25223,10 @@
         <v>1.0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S33" s="3">
         <v>8650.0</v>
@@ -24975,7 +25274,7 @@
         <v>0.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -25007,7 +25306,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>81</v>
@@ -25027,13 +25326,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>65</v>
@@ -25042,12 +25341,12 @@
         <v>88</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>81</v>
@@ -25076,7 +25375,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>81</v>
@@ -25088,7 +25387,7 @@
         <v>64</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S37" s="3">
         <v>13913.0</v>
@@ -25136,7 +25435,7 @@
         <v>5.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -25168,7 +25467,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>87</v>
@@ -25188,13 +25487,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>65</v>
@@ -25208,13 +25507,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>59</v>
@@ -25237,7 +25536,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>87</v>
@@ -25249,7 +25548,7 @@
         <v>64</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S41" s="3">
         <v>13277.0</v>
@@ -25297,7 +25596,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -25329,13 +25628,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -25349,13 +25648,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>59</v>
@@ -25378,13 +25677,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>65</v>
@@ -25398,7 +25697,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>92</v>
@@ -25407,10 +25706,10 @@
         <v>0.0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S45" s="3">
         <v>12722.0</v>
@@ -25458,7 +25757,7 @@
         <v>0.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AN45" s="3">
         <v>1.0</v>
@@ -25490,7 +25789,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>49</v>
@@ -25510,13 +25809,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>59</v>
@@ -25539,13 +25838,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>65</v>
@@ -25559,7 +25858,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
@@ -25619,7 +25918,7 @@
         <v>0.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -25651,7 +25950,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>63</v>
@@ -25671,13 +25970,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>51</v>
@@ -25700,7 +25999,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>63</v>
@@ -25760,7 +26059,7 @@
         <v>0.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -25792,13 +26091,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>65</v>
@@ -25812,7 +26111,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>69</v>
@@ -25845,7 +26144,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>69</v>
@@ -25855,7 +26154,7 @@
       <c r="E55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>51</v>
@@ -25869,7 +26168,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>69</v>
@@ -25927,7 +26226,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -25959,13 +26258,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>51</v>
@@ -25979,13 +26278,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>59</v>
@@ -26008,19 +26307,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>51</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>59</v>
@@ -26028,7 +26327,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>78</v>
@@ -26037,10 +26336,10 @@
         <v>0.0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S60" s="3">
         <v>18556.619999999995</v>
@@ -26088,7 +26387,7 @@
         <v>0.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AN60" s="3">
         <v>1.0</v>
@@ -26120,7 +26419,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>81</v>
@@ -26140,13 +26439,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>65</v>
@@ -26160,7 +26459,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>81</v>
@@ -26170,7 +26469,7 @@
       <c r="E63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>59</v>
@@ -26193,7 +26492,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>81</v>
@@ -26209,7 +26508,7 @@
         <v>64</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S64" s="3">
         <v>21825.50999999999</v>
@@ -26257,7 +26556,7 @@
         <v>0.0</v>
       </c>
       <c r="AM64" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AN64" s="3">
         <v>1.0</v>
@@ -26289,7 +26588,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>87</v>
@@ -26309,13 +26608,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>65</v>
@@ -26329,13 +26628,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>59</v>
@@ -26358,7 +26657,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>87</v>
@@ -26412,7 +26711,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -26444,13 +26743,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>51</v>
@@ -26464,13 +26763,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>59</v>
@@ -26493,7 +26792,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>92</v>
@@ -26547,7 +26846,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -26579,7 +26878,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -26599,13 +26898,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>59</v>
@@ -26628,7 +26927,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
@@ -26691,7 +26990,7 @@
         <v>0.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AN74" s="3">
         <v>1.0</v>
@@ -26723,7 +27022,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>63</v>
@@ -26743,13 +27042,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>59</v>
@@ -26758,7 +27057,7 @@
         <v>65</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M76" s="3">
         <v>2.0</v>
@@ -26772,13 +27071,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>65</v>
@@ -26801,7 +27100,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>63</v>
@@ -26861,7 +27160,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AN78" s="3">
         <v>2.0</v>
@@ -26893,13 +27192,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>51</v>
@@ -26913,13 +27212,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>59</v>
@@ -26942,7 +27241,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>69</v>
@@ -26971,7 +27270,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
@@ -26980,10 +27279,10 @@
         <v>0.0</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S82" s="3">
         <v>12752.009999999998</v>
@@ -27028,7 +27327,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AN82" s="3">
         <v>2.0</v>
@@ -27060,13 +27359,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>65</v>
@@ -27080,7 +27379,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>78</v>
@@ -27109,13 +27408,13 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>51</v>
@@ -27132,7 +27431,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>78</v>
@@ -27141,7 +27440,7 @@
         <v>0.0</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S86" s="3">
         <v>17035.32</v>
@@ -27189,7 +27488,7 @@
         <v>0.0</v>
       </c>
       <c r="AM86" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN86" s="3">
         <v>1.0</v>
@@ -27221,7 +27520,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>81</v>
@@ -27241,13 +27540,13 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>65</v>
@@ -27261,7 +27560,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>81</v>
@@ -27290,7 +27589,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>81</v>
@@ -27302,7 +27601,7 @@
         <v>64</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S90" s="3">
         <v>25392.46</v>
@@ -27350,7 +27649,7 @@
         <v>0.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AN90" s="3">
         <v>1.0</v>
@@ -27382,7 +27681,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>87</v>
@@ -27402,13 +27701,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>65</v>
@@ -27422,13 +27721,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>59</v>
@@ -27451,7 +27750,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>87</v>
@@ -27463,7 +27762,7 @@
         <v>64</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S94" s="3">
         <v>23475.639999999996</v>
@@ -27543,13 +27842,13 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>51</v>
@@ -27563,19 +27862,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>59</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>53</v>
@@ -27592,7 +27891,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>92</v>
@@ -27601,10 +27900,10 @@
         <v>0.0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S97" s="3">
         <v>19985.18999999999</v>
@@ -27652,7 +27951,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -27684,7 +27983,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -27704,13 +28003,13 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>51</v>
@@ -27727,13 +28026,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>59</v>
@@ -27756,7 +28055,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
@@ -27813,7 +28112,7 @@
         <v>0.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AN101" s="3">
         <v>1.0</v>
@@ -27845,13 +28144,13 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>65</v>
@@ -27865,13 +28164,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>51</v>
@@ -27888,7 +28187,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>63</v>
@@ -27917,7 +28216,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>63</v>
@@ -27926,7 +28225,7 @@
         <v>0.0</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S105" s="3">
         <v>12356.0</v>
@@ -27974,7 +28273,7 @@
         <v>0.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AN105" s="3">
         <v>1.0</v>
@@ -28006,13 +28305,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>65</v>
@@ -28026,13 +28325,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>51</v>
@@ -28049,7 +28348,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>69</v>
@@ -28078,7 +28377,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>69</v>
@@ -28087,7 +28386,7 @@
         <v>0.0</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S109" s="3">
         <v>8748.0</v>
@@ -28135,7 +28434,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -28167,13 +28466,13 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>65</v>
@@ -28187,7 +28486,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>78</v>
@@ -28216,13 +28515,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>51</v>
@@ -28245,7 +28544,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>78</v>
@@ -28299,7 +28598,7 @@
         <v>0.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN113" s="3">
         <v>2.0</v>
@@ -28331,13 +28630,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>65</v>
@@ -28351,7 +28650,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>81</v>
@@ -28371,13 +28670,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>59</v>
@@ -28400,13 +28699,13 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>51</v>
@@ -28423,7 +28722,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>81</v>
@@ -28432,7 +28731,7 @@
         <v>1.0</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S118" s="3">
         <v>22791.559999999998</v>
@@ -28480,7 +28779,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -28512,13 +28811,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>51</v>
@@ -28532,7 +28831,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>87</v>
@@ -28552,7 +28851,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>87</v>
@@ -28581,7 +28880,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>87</v>
@@ -28635,7 +28934,7 @@
         <v>0.0</v>
       </c>
       <c r="AM122" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AN122" s="3">
         <v>1.0</v>

--- a/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
+++ b/google_data/Pobočky/Prosek/Databaze Prosek 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3915" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3978" uniqueCount="442">
   <si>
     <t>Datum</t>
   </si>
@@ -379,6 +379,33 @@
     <t>11 min 15 s</t>
   </si>
   <si>
+    <t>18.06.2026</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>12 min 37 s</t>
+  </si>
+  <si>
+    <t>19.06.2026</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>12 min 38 s</t>
+  </si>
+  <si>
+    <t>20.06.2026</t>
+  </si>
+  <si>
+    <t>11 min 47 s</t>
+  </si>
+  <si>
     <t>01.05.2026</t>
   </si>
   <si>
@@ -460,9 +487,6 @@
     <t>11.05.2026</t>
   </si>
   <si>
-    <t>08:30</t>
-  </si>
-  <si>
     <t>12.05.2026</t>
   </si>
   <si>
@@ -490,9 +514,6 @@
     <t>Gorol Patrik</t>
   </si>
   <si>
-    <t>12 min 38 s</t>
-  </si>
-  <si>
     <t>16.05.2026</t>
   </si>
   <si>
@@ -508,9 +529,6 @@
     <t>Coufal Jakub</t>
   </si>
   <si>
-    <t>12 min 37 s</t>
-  </si>
-  <si>
     <t>18.05.2026</t>
   </si>
   <si>
@@ -538,9 +556,6 @@
     <t>23.05.2026</t>
   </si>
   <si>
-    <t>18:30</t>
-  </si>
-  <si>
     <t>24.05.2026</t>
   </si>
   <si>
@@ -670,9 +685,6 @@
     <t>Bušek Pavel</t>
   </si>
   <si>
-    <t>23:00</t>
-  </si>
-  <si>
     <t>11 min 19 s</t>
   </si>
   <si>
@@ -809,9 +821,6 @@
   </si>
   <si>
     <t>04.03.2026</t>
-  </si>
-  <si>
-    <t>11 min 47 s</t>
   </si>
   <si>
     <t>05.03.2026</t>
@@ -4438,6 +4447,448 @@
         <v>0.15384615384615385</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P70" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S70" s="3">
+        <v>18979.40000000001</v>
+      </c>
+      <c r="T70" s="3">
+        <v>4988.0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>3350.0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>3649.1</v>
+      </c>
+      <c r="W70" s="3">
+        <v>1095.0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>5500.0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>452.0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>39286.99999999999</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>-0.4999999999854481</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0.2759398681497697</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>700.0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>573.0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM70" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN70" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>106.0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR70" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS70" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="AT70" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AU70" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="AV70" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="P74" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="S74" s="3">
+        <v>19656.400000000005</v>
+      </c>
+      <c r="T74" s="3">
+        <v>8417.0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>6868.0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>5146.0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>1193.0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>3129.0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>1806.0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>46215.399999999994</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>1.4551915228366852E-11</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0.21344165278240593</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>738.0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM74" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>122.0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR74" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS74" s="3">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AT74" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU74" s="3">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AV74" s="3">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P78" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S78" s="3">
+        <v>21164.800000000003</v>
+      </c>
+      <c r="T78" s="3">
+        <v>5399.0</v>
+      </c>
+      <c r="U78" s="3">
+        <v>7468.0</v>
+      </c>
+      <c r="V78" s="3">
+        <v>7130.0</v>
+      </c>
+      <c r="W78" s="3">
+        <v>925.0</v>
+      </c>
+      <c r="X78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y78" s="3">
+        <v>1456.0</v>
+      </c>
+      <c r="AA78" s="3">
+        <v>1650.0</v>
+      </c>
+      <c r="AB78" s="3">
+        <v>45194.29999999998</v>
+      </c>
+      <c r="AC78" s="3">
+        <v>-1.4999999999781721</v>
+      </c>
+      <c r="AD78" s="3">
+        <v>0.21506974817620822</v>
+      </c>
+      <c r="AI78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL78" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AM78" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN78" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO78" s="3">
+        <v>108.0</v>
+      </c>
+      <c r="AP78" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="AQ78" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR78" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS78" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="AT78" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AU78" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AV78" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4598,19 +5049,19 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>59</v>
@@ -4618,7 +5069,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>81</v>
@@ -4630,7 +5081,7 @@
         <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>59</v>
@@ -4638,7 +5089,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>81</v>
@@ -4661,7 +5112,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>81</v>
@@ -4670,7 +5121,7 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>54</v>
@@ -4721,7 +5172,7 @@
         <v>2.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="AN5" s="3">
         <v>0.0</v>
@@ -4753,7 +5204,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>87</v>
@@ -4773,13 +5224,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>65</v>
@@ -4793,7 +5244,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>87</v>
@@ -4853,7 +5304,7 @@
         <v>0.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AN8" s="3">
         <v>0.0</v>
@@ -4885,13 +5336,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>51</v>
@@ -4905,7 +5356,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>92</v>
@@ -4925,13 +5376,13 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>59</v>
@@ -4940,7 +5391,7 @@
         <v>65</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M11" s="3">
         <v>3.0</v>
@@ -4954,7 +5405,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>92</v>
@@ -4963,7 +5414,7 @@
         <v>8.0</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>64</v>
@@ -5014,7 +5465,7 @@
         <v>1.0</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AN12" s="3">
         <v>1.0</v>
@@ -5046,13 +5497,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>59</v>
@@ -5066,7 +5517,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -5086,7 +5537,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -5095,7 +5546,7 @@
         <v>5.0</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>54</v>
@@ -5146,7 +5597,7 @@
         <v>1.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="AN15" s="3">
         <v>0.0</v>
@@ -5178,7 +5629,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -5198,7 +5649,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>63</v>
@@ -5227,7 +5678,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>63</v>
@@ -5287,7 +5738,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -5319,13 +5770,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>51</v>
@@ -5339,7 +5790,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>69</v>
@@ -5359,7 +5810,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>69</v>
@@ -5392,7 +5843,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>69</v>
@@ -5405,7 +5856,7 @@
         <v>0.0</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>64</v>
@@ -5459,7 +5910,7 @@
         <v>1.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -5491,7 +5942,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>78</v>
@@ -5511,7 +5962,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>78</v>
@@ -5531,7 +5982,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>78</v>
@@ -5560,7 +6011,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>78</v>
@@ -5623,7 +6074,7 @@
         <v>0.0</v>
       </c>
       <c r="AM26" s="1" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="AN26" s="3">
         <v>1.0</v>
@@ -5655,7 +6106,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>81</v>
@@ -5675,7 +6126,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>81</v>
@@ -5695,7 +6146,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>81</v>
@@ -5728,7 +6179,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>81</v>
@@ -5798,7 +6249,7 @@
         <v>0.0</v>
       </c>
       <c r="AM30" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="AN30" s="3">
         <v>1.0</v>
@@ -5830,13 +6281,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>51</v>
@@ -5850,7 +6301,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>87</v>
@@ -5870,13 +6321,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>65</v>
@@ -5890,13 +6341,13 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>51</v>
@@ -5919,7 +6370,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>87</v>
@@ -5928,7 +6379,7 @@
         <v>7.0</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>54</v>
@@ -5982,7 +6433,7 @@
         <v>1.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="AN35" s="3">
         <v>1.0</v>
@@ -6014,13 +6465,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>51</v>
@@ -6034,7 +6485,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>92</v>
@@ -6054,13 +6505,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>59</v>
@@ -6069,7 +6520,7 @@
         <v>65</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M38" s="3">
         <v>2.0</v>
@@ -6083,7 +6534,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>92</v>
@@ -6092,7 +6543,7 @@
         <v>9.0</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>54</v>
@@ -6146,7 +6597,7 @@
         <v>0.0</v>
       </c>
       <c r="AM39" s="1" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="AN39" s="3">
         <v>1.0</v>
@@ -6178,7 +6629,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
@@ -6198,13 +6649,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>65</v>
@@ -6213,12 +6664,12 @@
         <v>73</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>49</v>
@@ -6230,7 +6681,7 @@
         <v>64</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="S42" s="3">
         <v>11900.0</v>
@@ -6310,7 +6761,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>63</v>
@@ -6330,7 +6781,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>63</v>
@@ -6359,7 +6810,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>63</v>
@@ -6419,7 +6870,7 @@
         <v>5.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="AN45" s="3">
         <v>1.0</v>
@@ -6451,7 +6902,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>69</v>
@@ -6471,7 +6922,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>69</v>
@@ -6491,7 +6942,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>69</v>
@@ -6520,7 +6971,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>69</v>
@@ -6580,7 +7031,7 @@
         <v>1.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -6612,13 +7063,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>51</v>
@@ -6632,7 +7083,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>78</v>
@@ -6661,7 +7112,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>78</v>
@@ -6670,10 +7121,10 @@
         <v>0.0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="S52" s="3">
         <v>9727.0</v>
@@ -6721,7 +7172,7 @@
         <v>1.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -6753,7 +7204,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>81</v>
@@ -6765,7 +7216,7 @@
         <v>51</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>51</v>
@@ -6773,16 +7224,16 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>83</v>
@@ -6793,13 +7244,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>65</v>
@@ -6813,7 +7264,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>81</v>
@@ -6842,7 +7293,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>81</v>
@@ -6854,7 +7305,7 @@
         <v>64</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="S57" s="3">
         <v>21791.6</v>
@@ -6902,7 +7353,7 @@
         <v>0.0</v>
       </c>
       <c r="AM57" s="1" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="AN57" s="3">
         <v>1.0</v>
@@ -6934,7 +7385,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>87</v>
@@ -6954,13 +7405,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>55</v>
@@ -6977,7 +7428,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>87</v>
@@ -7037,7 +7488,7 @@
         <v>7.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="AN60" s="3">
         <v>0.0</v>
@@ -7069,7 +7520,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>92</v>
@@ -7089,13 +7540,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>51</v>
@@ -7109,7 +7560,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>92</v>
@@ -7170,7 +7621,7 @@
         <v>2.0</v>
       </c>
       <c r="AM63" s="1" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="AN63" s="3">
         <v>0.0</v>
@@ -7202,7 +7653,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -7222,7 +7673,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -7314,13 +7765,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>51</v>
@@ -7334,7 +7785,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>63</v>
@@ -7354,7 +7805,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>63</v>
@@ -7383,7 +7834,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>63</v>
@@ -7392,7 +7843,7 @@
         <v>2.0</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>54</v>
@@ -7446,7 +7897,7 @@
         <v>2.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AN69" s="3">
         <v>1.0</v>
@@ -7478,7 +7929,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
@@ -7498,7 +7949,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>69</v>
@@ -7527,7 +7978,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>69</v>
@@ -7619,7 +8070,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>78</v>
@@ -7639,7 +8090,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>78</v>
@@ -7659,7 +8110,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>78</v>
@@ -7679,7 +8130,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>78</v>
@@ -7708,7 +8159,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>78</v>
@@ -7768,7 +8219,7 @@
         <v>1.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AN77" s="3">
         <v>1.0</v>
@@ -7800,7 +8251,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>81</v>
@@ -7820,7 +8271,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>81</v>
@@ -7849,7 +8300,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>81</v>
@@ -7912,7 +8363,7 @@
         <v>1.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AN80" s="3">
         <v>1.0</v>
@@ -7944,7 +8395,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>87</v>
@@ -7953,24 +8404,24 @@
         <v>54</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>51</v>
@@ -7984,7 +8435,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>87</v>
@@ -8013,7 +8464,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>87</v>
@@ -8022,7 +8473,7 @@
         <v>2.0</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="R84" s="1" t="s">
         <v>54</v>
@@ -8105,7 +8556,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>92</v>
@@ -8125,7 +8576,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>92</v>
@@ -8145,7 +8596,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>92</v>
@@ -8174,7 +8625,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>92</v>
@@ -8234,7 +8685,7 @@
         <v>3.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -8266,7 +8717,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -8286,7 +8737,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -8315,7 +8766,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -8378,7 +8829,7 @@
         <v>4.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -8410,7 +8861,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>63</v>
@@ -8430,7 +8881,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>63</v>
@@ -8450,7 +8901,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>63</v>
@@ -8470,7 +8921,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>63</v>
@@ -8533,7 +8984,7 @@
         <v>1.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AN95" s="3">
         <v>0.0</v>
@@ -8565,7 +9016,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
@@ -8585,7 +9036,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -8605,7 +9056,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>69</v>
@@ -8634,7 +9085,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>69</v>
@@ -8694,7 +9145,7 @@
         <v>2.0</v>
       </c>
       <c r="AM99" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AN99" s="3">
         <v>1.0</v>
@@ -8726,7 +9177,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>78</v>
@@ -8746,7 +9197,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>78</v>
@@ -8766,7 +9217,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>78</v>
@@ -8786,7 +9237,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>78</v>
@@ -8815,7 +9266,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>78</v>
@@ -8878,7 +9329,7 @@
         <v>1.0</v>
       </c>
       <c r="AM104" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AN104" s="3">
         <v>1.0</v>
@@ -8910,7 +9361,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>81</v>
@@ -8930,7 +9381,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>81</v>
@@ -8950,7 +9401,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>81</v>
@@ -8970,7 +9421,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>81</v>
@@ -8999,7 +9450,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>81</v>
@@ -9059,7 +9510,7 @@
         <v>1.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -9091,7 +9542,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>87</v>
@@ -9111,7 +9562,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>87</v>
@@ -9120,7 +9571,7 @@
         <v>54</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>83</v>
@@ -9131,7 +9582,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>87</v>
@@ -9160,7 +9611,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>87</v>
@@ -9223,7 +9674,7 @@
         <v>0.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AN113" s="3">
         <v>1.0</v>
@@ -9255,7 +9706,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>92</v>
@@ -9275,7 +9726,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>92</v>
@@ -9290,12 +9741,12 @@
         <v>84</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>92</v>
@@ -9315,7 +9766,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>92</v>
@@ -9344,7 +9795,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>92</v>
@@ -9404,7 +9855,7 @@
         <v>3.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -9594,13 +10045,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -9614,7 +10065,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>69</v>
@@ -9634,7 +10085,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
@@ -9663,7 +10114,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>69</v>
@@ -9672,7 +10123,7 @@
         <v>2.0</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>54</v>
@@ -9729,7 +10180,7 @@
         <v>1.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -9761,7 +10212,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>78</v>
@@ -9781,7 +10232,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>78</v>
@@ -9810,7 +10261,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>78</v>
@@ -9873,7 +10324,7 @@
         <v>0.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AN8" s="3">
         <v>1.0</v>
@@ -9905,7 +10356,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>81</v>
@@ -9925,7 +10376,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>81</v>
@@ -9935,7 +10386,7 @@
       <c r="E10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>104</v>
@@ -9952,7 +10403,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>81</v>
@@ -10019,7 +10470,7 @@
         <v>3.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
@@ -10051,7 +10502,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>87</v>
@@ -10071,13 +10522,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>59</v>
@@ -10100,7 +10551,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>87</v>
@@ -10163,7 +10614,7 @@
         <v>2.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -10195,7 +10646,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>92</v>
@@ -10215,13 +10666,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>59</v>
@@ -10244,7 +10695,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>92</v>
@@ -10304,7 +10755,7 @@
         <v>0.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AN17" s="3">
         <v>1.0</v>
@@ -10336,7 +10787,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>49</v>
@@ -10356,7 +10807,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
@@ -10376,7 +10827,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
@@ -10405,7 +10856,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
@@ -10468,7 +10919,7 @@
         <v>3.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -10500,13 +10951,13 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>51</v>
@@ -10520,7 +10971,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>63</v>
@@ -10540,7 +10991,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>63</v>
@@ -10569,7 +11020,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>63</v>
@@ -10578,7 +11029,7 @@
         <v>0.0</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>64</v>
@@ -10632,7 +11083,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -10664,13 +11115,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>51</v>
@@ -10684,7 +11135,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>69</v>
@@ -10704,7 +11155,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>69</v>
@@ -10733,7 +11184,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>69</v>
@@ -10742,7 +11193,7 @@
         <v>1.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>54</v>
@@ -10793,7 +11244,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -10825,7 +11276,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>78</v>
@@ -10845,7 +11296,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>78</v>
@@ -10865,7 +11316,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>78</v>
@@ -10894,7 +11345,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>78</v>
@@ -10954,7 +11405,7 @@
         <v>2.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -10986,7 +11437,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>81</v>
@@ -11006,13 +11457,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>71</v>
@@ -11021,12 +11472,12 @@
         <v>52</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>81</v>
@@ -11055,7 +11506,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>81</v>
@@ -11118,7 +11569,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -11150,33 +11601,33 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>65</v>
@@ -11185,24 +11636,24 @@
         <v>88</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>217</v>
+        <v>121</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>82</v>
@@ -11210,7 +11661,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>87</v>
@@ -11223,10 +11674,10 @@
         <v>9.0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="S41" s="3">
         <v>17084.0</v>
@@ -11274,7 +11725,7 @@
         <v>2.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AN41" s="3">
         <v>0.0</v>
@@ -11306,13 +11757,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -11326,7 +11777,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>92</v>
@@ -11346,7 +11797,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>92</v>
@@ -11366,7 +11817,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>92</v>
@@ -11376,7 +11827,7 @@
       <c r="E45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>65</v>
@@ -11393,7 +11844,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>92</v>
@@ -11406,7 +11857,7 @@
         <v>2.0</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>54</v>
@@ -11463,7 +11914,7 @@
         <v>1.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AN46" s="3">
         <v>0.0</v>
@@ -11495,13 +11946,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>51</v>
@@ -11515,7 +11966,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
@@ -11535,7 +11986,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
@@ -11564,7 +12015,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
@@ -11573,7 +12024,7 @@
         <v>2.0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>54</v>
@@ -11624,7 +12075,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -11656,13 +12107,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>51</v>
@@ -11676,7 +12127,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>63</v>
@@ -11696,7 +12147,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>63</v>
@@ -11725,7 +12176,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>63</v>
@@ -11734,7 +12185,7 @@
         <v>1.0</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R54" s="1" t="s">
         <v>54</v>
@@ -11794,7 +12245,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -11826,19 +12277,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>74</v>
@@ -11846,7 +12297,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>69</v>
@@ -11866,7 +12317,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>69</v>
@@ -11878,10 +12329,10 @@
         <v>51</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="M57" s="3">
         <v>1.0</v>
@@ -11895,22 +12346,22 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M58" s="3">
         <v>3.0</v>
@@ -11924,7 +12375,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>69</v>
@@ -11933,7 +12384,7 @@
         <v>0.0</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>54</v>
@@ -11984,7 +12435,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AN59" s="3">
         <v>2.0</v>
@@ -12016,7 +12467,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>78</v>
@@ -12036,7 +12487,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>78</v>
@@ -12065,7 +12516,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>78</v>
@@ -12125,7 +12576,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -12157,7 +12608,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>81</v>
@@ -12177,7 +12628,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>81</v>
@@ -12197,7 +12648,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>81</v>
@@ -12207,7 +12658,7 @@
       <c r="E65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>59</v>
@@ -12216,7 +12667,7 @@
         <v>65</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M65" s="3">
         <v>3.0</v>
@@ -12230,7 +12681,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>81</v>
@@ -12297,7 +12748,7 @@
         <v>0.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -12329,13 +12780,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>51</v>
@@ -12349,7 +12800,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>87</v>
@@ -12369,7 +12820,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>87</v>
@@ -12384,18 +12835,18 @@
         <v>88</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>59</v>
@@ -12404,7 +12855,7 @@
         <v>65</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M70" s="3">
         <v>6.0</v>
@@ -12418,7 +12869,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>87</v>
@@ -12427,7 +12878,7 @@
         <v>8.0</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>54</v>
@@ -12478,7 +12929,7 @@
         <v>2.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -12510,7 +12961,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>92</v>
@@ -12530,7 +12981,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>92</v>
@@ -12550,7 +13001,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>92</v>
@@ -12613,7 +13064,7 @@
         <v>2.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AN74" s="3">
         <v>0.0</v>
@@ -12645,19 +13096,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>74</v>
@@ -12665,7 +13116,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
@@ -12685,7 +13136,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -12714,7 +13165,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>49</v>
@@ -12723,7 +13174,7 @@
         <v>0.0</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>54</v>
@@ -12777,7 +13228,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AN78" s="3">
         <v>1.0</v>
@@ -12809,7 +13260,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>63</v>
@@ -12829,7 +13280,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>63</v>
@@ -12858,7 +13309,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>63</v>
@@ -12921,7 +13372,7 @@
         <v>1.0</v>
       </c>
       <c r="AM81" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AN81" s="3">
         <v>1.0</v>
@@ -12953,13 +13404,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>51</v>
@@ -12973,7 +13424,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>69</v>
@@ -12993,7 +13444,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>69</v>
@@ -13008,7 +13459,7 @@
         <v>109</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="M84" s="3">
         <v>1.0</v>
@@ -13022,7 +13473,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>69</v>
@@ -13031,7 +13482,7 @@
         <v>8.0</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>64</v>
@@ -13082,7 +13533,7 @@
         <v>1.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN85" s="3">
         <v>1.0</v>
@@ -13114,7 +13565,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>78</v>
@@ -13134,7 +13585,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>78</v>
@@ -13163,7 +13614,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>78</v>
@@ -13223,7 +13674,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AN88" s="3">
         <v>1.0</v>
@@ -13255,7 +13706,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>81</v>
@@ -13275,13 +13726,13 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>59</v>
@@ -13290,7 +13741,7 @@
         <v>65</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M90" s="3">
         <v>6.0</v>
@@ -13304,7 +13755,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>81</v>
@@ -13364,7 +13815,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -13396,7 +13847,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>87</v>
@@ -13416,13 +13867,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>59</v>
@@ -13431,7 +13882,7 @@
         <v>65</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M93" s="3">
         <v>4.0</v>
@@ -13445,13 +13896,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>65</v>
@@ -13474,7 +13925,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>87</v>
@@ -13534,7 +13985,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AN95" s="3">
         <v>2.0</v>
@@ -13566,7 +14017,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>92</v>
@@ -13586,7 +14037,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>92</v>
@@ -13646,7 +14097,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -13678,7 +14129,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -13698,7 +14149,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -13713,7 +14164,7 @@
         <v>109</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="N99" s="1" t="b">
         <v>1</v>
@@ -13721,7 +14172,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -13781,7 +14232,7 @@
         <v>0.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AN100" s="3">
         <v>0.0</v>
@@ -13813,7 +14264,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>63</v>
@@ -13833,7 +14284,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>63</v>
@@ -13853,7 +14304,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>63</v>
@@ -13913,7 +14364,7 @@
         <v>1.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AN103" s="3">
         <v>0.0</v>
@@ -13945,7 +14396,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>69</v>
@@ -13965,7 +14416,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>69</v>
@@ -13974,13 +14425,13 @@
         <v>58</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="M105" s="3">
         <v>8.0</v>
@@ -13988,7 +14439,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>69</v>
@@ -14054,7 +14505,7 @@
         <v>2.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AN106" s="3">
         <v>0.0</v>
@@ -14086,7 +14537,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>78</v>
@@ -14106,7 +14557,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>78</v>
@@ -14121,7 +14572,7 @@
         <v>73</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="M108" s="3">
         <v>9.0</v>
@@ -14129,7 +14580,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>78</v>
@@ -14189,7 +14640,7 @@
         <v>2.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AN109" s="3">
         <v>0.0</v>
@@ -14379,7 +14830,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>92</v>
@@ -14399,7 +14850,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>92</v>
@@ -14419,13 +14870,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>59</v>
@@ -14448,7 +14899,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>92</v>
@@ -14511,7 +14962,7 @@
         <v>5.0</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AN5" s="3">
         <v>1.0</v>
@@ -14543,7 +14994,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>49</v>
@@ -14563,7 +15014,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>49</v>
@@ -14583,13 +15034,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>51</v>
@@ -14603,7 +15054,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -14632,7 +15083,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -14692,7 +15143,7 @@
         <v>0.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AN10" s="3">
         <v>1.0</v>
@@ -14724,7 +15175,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>63</v>
@@ -14744,13 +15195,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>59</v>
@@ -14773,7 +15224,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>63</v>
@@ -14836,7 +15287,7 @@
         <v>3.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AN13" s="3">
         <v>1.0</v>
@@ -14868,7 +15319,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>69</v>
@@ -14888,13 +15339,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -14908,7 +15359,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
@@ -14928,7 +15379,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>69</v>
@@ -14951,7 +15402,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>69</v>
@@ -15014,7 +15465,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>264</v>
+        <v>128</v>
       </c>
       <c r="AN18" s="3">
         <v>0.0</v>
@@ -15046,7 +15497,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>78</v>
@@ -15066,7 +15517,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>78</v>
@@ -15086,7 +15537,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>78</v>
@@ -15109,7 +15560,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>78</v>
@@ -15175,7 +15626,7 @@
         <v>2.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN22" s="3">
         <v>0.0</v>
@@ -15207,7 +15658,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>81</v>
@@ -15227,7 +15678,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>81</v>
@@ -15237,7 +15688,7 @@
       <c r="E24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>51</v>
@@ -15260,7 +15711,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>81</v>
@@ -15324,7 +15775,7 @@
         <v>3.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -15356,13 +15807,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>51</v>
@@ -15376,13 +15827,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>109</v>
@@ -15396,7 +15847,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>87</v>
@@ -15406,7 +15857,7 @@
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>59</v>
@@ -15429,7 +15880,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>87</v>
@@ -15442,10 +15893,10 @@
         <v>5.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="S29" s="3">
         <v>13413.0</v>
@@ -15493,7 +15944,7 @@
         <v>7.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -15525,13 +15976,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>51</v>
@@ -15540,12 +15991,12 @@
         <v>55</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>92</v>
@@ -15555,7 +16006,7 @@
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>59</v>
@@ -15578,7 +16029,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>92</v>
@@ -15591,10 +16042,10 @@
         <v>3.0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="S32" s="3">
         <v>12040.0</v>
@@ -15645,7 +16096,7 @@
         <v>9.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN32" s="3">
         <v>1.0</v>
@@ -15677,7 +16128,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
@@ -15697,7 +16148,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -15726,7 +16177,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
@@ -15786,7 +16237,7 @@
         <v>0.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AN35" s="3">
         <v>1.0</v>
@@ -15818,7 +16269,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>63</v>
@@ -15838,7 +16289,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>63</v>
@@ -15867,7 +16318,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>63</v>
@@ -15927,7 +16378,7 @@
         <v>0.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AN38" s="3">
         <v>1.0</v>
@@ -15959,13 +16410,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>51</v>
@@ -15979,7 +16430,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>69</v>
@@ -15999,33 +16450,33 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>51</v>
@@ -16039,7 +16490,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
@@ -16068,7 +16519,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
@@ -16077,7 +16528,7 @@
         <v>0.0</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>54</v>
@@ -16128,7 +16579,7 @@
         <v>1.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -16160,13 +16611,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>51</v>
@@ -16180,7 +16631,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>78</v>
@@ -16200,27 +16651,27 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>78</v>
@@ -16230,7 +16681,7 @@
       <c r="E48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>59</v>
@@ -16239,12 +16690,12 @@
         <v>65</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>78</v>
@@ -16277,7 +16728,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>78</v>
@@ -16290,7 +16741,7 @@
         <v>0.0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>54</v>
@@ -16344,7 +16795,7 @@
         <v>1.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -16376,7 +16827,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>81</v>
@@ -16388,7 +16839,7 @@
         <v>51</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>217</v>
+        <v>121</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>93</v>
@@ -16396,7 +16847,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>81</v>
@@ -16416,13 +16867,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>59</v>
@@ -16439,7 +16890,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>81</v>
@@ -16502,7 +16953,7 @@
         <v>3.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN54" s="3">
         <v>0.0</v>
@@ -16534,7 +16985,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>87</v>
@@ -16554,7 +17005,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>87</v>
@@ -16566,30 +17017,30 @@
         <v>65</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>59</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M57" s="3">
         <v>13.0</v>
@@ -16597,7 +17048,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>87</v>
@@ -16660,7 +17111,7 @@
         <v>5.0</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AN58" s="3">
         <v>0.0</v>
@@ -16692,7 +17143,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>92</v>
@@ -16712,13 +17163,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>59</v>
@@ -16735,7 +17186,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>92</v>
@@ -16795,7 +17246,7 @@
         <v>6.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AN61" s="3">
         <v>0.0</v>
@@ -16827,13 +17278,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>51</v>
@@ -16847,7 +17298,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -16867,7 +17318,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -16879,7 +17330,7 @@
         <v>59</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>217</v>
+        <v>121</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>53</v>
@@ -16896,7 +17347,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -16905,7 +17356,7 @@
         <v>1.0</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R65" s="1" t="s">
         <v>54</v>
@@ -16956,7 +17407,7 @@
         <v>2.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -16988,7 +17439,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>63</v>
@@ -17008,7 +17459,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>63</v>
@@ -17037,7 +17488,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>63</v>
@@ -17097,7 +17548,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -17129,7 +17580,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>69</v>
@@ -17149,7 +17600,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
@@ -17178,7 +17629,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>69</v>
@@ -17238,7 +17689,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -17270,13 +17721,13 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>51</v>
@@ -17290,7 +17741,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>78</v>
@@ -17310,13 +17761,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>71</v>
@@ -17325,12 +17776,12 @@
         <v>52</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>78</v>
@@ -17359,7 +17810,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>78</v>
@@ -17368,7 +17819,7 @@
         <v>2.0</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>54</v>
@@ -17422,7 +17873,7 @@
         <v>0.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -17454,7 +17905,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>81</v>
@@ -17474,7 +17925,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>81</v>
@@ -17494,7 +17945,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>81</v>
@@ -17554,7 +18005,7 @@
         <v>4.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AN79" s="3">
         <v>0.0</v>
@@ -17586,19 +18037,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>74</v>
@@ -17606,7 +18057,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>87</v>
@@ -17626,7 +18077,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>87</v>
@@ -17638,15 +18089,15 @@
         <v>55</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>87</v>
@@ -17655,7 +18106,7 @@
         <v>15.0</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R83" s="1" t="s">
         <v>54</v>
@@ -17706,7 +18157,7 @@
         <v>5.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -17738,7 +18189,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>92</v>
@@ -17758,7 +18209,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>92</v>
@@ -17818,7 +18269,7 @@
         <v>2.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AN85" s="3">
         <v>0.0</v>
@@ -17850,7 +18301,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
@@ -17870,7 +18321,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -17890,7 +18341,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -17919,7 +18370,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -17979,7 +18430,7 @@
         <v>0.0</v>
       </c>
       <c r="AM89" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN89" s="3">
         <v>1.0</v>
@@ -18011,19 +18462,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>74</v>
@@ -18031,7 +18482,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>63</v>
@@ -18051,7 +18502,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>63</v>
@@ -18080,7 +18531,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>63</v>
@@ -18089,7 +18540,7 @@
         <v>2.0</v>
       </c>
       <c r="Q93" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R93" s="1" t="s">
         <v>54</v>
@@ -18143,7 +18594,7 @@
         <v>0.0</v>
       </c>
       <c r="AM93" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AN93" s="3">
         <v>1.0</v>
@@ -18175,19 +18626,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>74</v>
@@ -18195,7 +18646,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>69</v>
@@ -18215,7 +18666,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>69</v>
@@ -18244,7 +18695,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>69</v>
@@ -18253,7 +18704,7 @@
         <v>2.0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R97" s="1" t="s">
         <v>54</v>
@@ -18339,7 +18790,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>78</v>
@@ -18359,7 +18810,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>78</v>
@@ -18388,7 +18839,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>78</v>
@@ -18451,7 +18902,7 @@
         <v>2.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AN100" s="3">
         <v>1.0</v>
@@ -18483,7 +18934,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>81</v>
@@ -18503,13 +18954,13 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>104</v>
@@ -18523,7 +18974,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>81</v>
@@ -18583,7 +19034,7 @@
         <v>4.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AN103" s="3">
         <v>0.0</v>
@@ -18615,27 +19066,27 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>87</v>
@@ -18655,33 +19106,33 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>53</v>
@@ -18704,13 +19155,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>59</v>
@@ -18719,7 +19170,7 @@
         <v>65</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="N108" s="1" t="b">
         <v>1</v>
@@ -18727,7 +19178,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>87</v>
@@ -18736,7 +19187,7 @@
         <v>1.0</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>54</v>
@@ -18790,7 +19241,7 @@
         <v>1.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -18822,7 +19273,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>92</v>
@@ -18842,7 +19293,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>92</v>
@@ -18862,7 +19313,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>92</v>
@@ -18882,7 +19333,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>92</v>
@@ -18946,7 +19397,7 @@
         <v>3.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AN113" s="3">
         <v>0.0</v>
@@ -18978,7 +19429,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -18998,7 +19449,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
@@ -19018,13 +19469,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>65</v>
@@ -19038,7 +19489,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
@@ -19067,7 +19518,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -19130,7 +19581,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -19162,13 +19613,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>51</v>
@@ -19182,7 +19633,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>63</v>
@@ -19202,13 +19653,13 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>51</v>
@@ -19225,7 +19676,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>63</v>
@@ -19254,7 +19705,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>63</v>
@@ -19263,7 +19714,7 @@
         <v>0.0</v>
       </c>
       <c r="Q123" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="R123" s="1" t="s">
         <v>54</v>
@@ -19320,7 +19771,7 @@
         <v>0.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -19510,13 +19961,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -19530,13 +19981,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>59</v>
@@ -19559,7 +20010,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>92</v>
@@ -19613,7 +20064,7 @@
         <v>0.0</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AN4" s="3">
         <v>1.0</v>
@@ -19645,7 +20096,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>49</v>
@@ -19665,7 +20116,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>49</v>
@@ -19694,7 +20145,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>49</v>
@@ -19754,7 +20205,7 @@
         <v>1.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AN7" s="3">
         <v>1.0</v>
@@ -19786,7 +20237,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>63</v>
@@ -19806,13 +20257,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>59</v>
@@ -19835,13 +20286,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>51</v>
@@ -19858,7 +20309,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>63</v>
@@ -19915,7 +20366,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -19947,13 +20398,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>51</v>
@@ -19967,13 +20418,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>59</v>
@@ -19996,7 +20447,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>69</v>
@@ -20005,10 +20456,10 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S14" s="3">
         <v>15925.179999999997</v>
@@ -20056,7 +20507,7 @@
         <v>0.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -20088,7 +20539,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>78</v>
@@ -20108,13 +20559,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>51</v>
@@ -20131,7 +20582,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>78</v>
@@ -20160,7 +20611,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>78</v>
@@ -20217,7 +20668,7 @@
         <v>0.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -20249,13 +20700,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>51</v>
@@ -20269,7 +20720,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>81</v>
@@ -20289,7 +20740,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>81</v>
@@ -20318,7 +20769,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>81</v>
@@ -20372,7 +20823,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -20404,13 +20855,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>51</v>
@@ -20424,19 +20875,19 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>59</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>217</v>
+        <v>121</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>53</v>
@@ -20453,13 +20904,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>65</v>
@@ -20476,13 +20927,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>59</v>
@@ -20505,7 +20956,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>87</v>
@@ -20559,7 +21010,7 @@
         <v>1.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AN27" s="3">
         <v>2.0</v>
@@ -20591,13 +21042,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>51</v>
@@ -20611,13 +21062,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>109</v>
@@ -20640,13 +21091,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>59</v>
@@ -20655,7 +21106,7 @@
         <v>109</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="M30" s="3">
         <v>1.0</v>
@@ -20669,13 +21120,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>109</v>
@@ -20698,7 +21149,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>92</v>
@@ -20707,10 +21158,10 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S32" s="3">
         <v>9567.0</v>
@@ -20758,7 +21209,7 @@
         <v>0.0</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AN32" s="3">
         <v>3.0</v>
@@ -20790,13 +21241,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>51</v>
@@ -20810,7 +21261,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -20830,13 +21281,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>59</v>
@@ -20845,7 +21296,7 @@
         <v>65</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M35" s="3">
         <v>1.0</v>
@@ -20859,13 +21310,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>109</v>
@@ -20888,7 +21339,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -20897,7 +21348,7 @@
         <v>1.0</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>64</v>
@@ -20948,7 +21399,7 @@
         <v>0.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AN37" s="3">
         <v>2.0</v>
@@ -20980,13 +21431,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
@@ -21000,13 +21451,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>59</v>
@@ -21015,7 +21466,7 @@
         <v>65</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M39" s="3">
         <v>2.0</v>
@@ -21029,13 +21480,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>65</v>
@@ -21058,7 +21509,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>63</v>
@@ -21067,10 +21518,10 @@
         <v>0.0</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S41" s="3">
         <v>6459.0</v>
@@ -21118,7 +21569,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -21150,7 +21601,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>69</v>
@@ -21170,7 +21621,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>69</v>
@@ -21199,7 +21650,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>69</v>
@@ -21259,7 +21710,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AN44" s="3">
         <v>1.0</v>
@@ -21291,7 +21742,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>78</v>
@@ -21311,13 +21762,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>51</v>
@@ -21334,7 +21785,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>78</v>
@@ -21363,7 +21814,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>78</v>
@@ -21423,7 +21874,7 @@
         <v>1.0</v>
       </c>
       <c r="AM48" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AN48" s="3">
         <v>1.0</v>
@@ -21455,13 +21906,13 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>51</v>
@@ -21475,7 +21926,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>81</v>
@@ -21495,7 +21946,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>81</v>
@@ -21524,7 +21975,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>81</v>
@@ -21533,10 +21984,10 @@
         <v>1.0</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S52" s="3">
         <v>23294.0</v>
@@ -21581,7 +22032,7 @@
         <v>4.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -21613,13 +22064,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>75</v>
@@ -21633,7 +22084,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>87</v>
@@ -21653,13 +22104,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>59</v>
@@ -21682,7 +22133,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>87</v>
@@ -21736,7 +22187,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -21768,7 +22219,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>92</v>
@@ -21788,7 +22239,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>92</v>
@@ -21808,7 +22259,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>92</v>
@@ -21871,7 +22322,7 @@
         <v>0.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AN59" s="3">
         <v>0.0</v>
@@ -21903,13 +22354,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>51</v>
@@ -21926,7 +22377,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -21955,7 +22406,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
@@ -22009,7 +22460,7 @@
         <v>1.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -22041,7 +22492,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>63</v>
@@ -22061,13 +22512,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>51</v>
@@ -22084,7 +22535,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>63</v>
@@ -22113,7 +22564,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>63</v>
@@ -22170,7 +22621,7 @@
         <v>1.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN66" s="3">
         <v>1.0</v>
@@ -22202,7 +22653,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>69</v>
@@ -22222,7 +22673,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>69</v>
@@ -22251,7 +22702,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>69</v>
@@ -22311,7 +22762,7 @@
         <v>0.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN69" s="3">
         <v>1.0</v>
@@ -22343,7 +22794,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>78</v>
@@ -22363,7 +22814,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>78</v>
@@ -22392,7 +22843,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>78</v>
@@ -22452,7 +22903,7 @@
         <v>0.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="AN72" s="3">
         <v>1.0</v>
@@ -22484,7 +22935,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>81</v>
@@ -22504,7 +22955,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>81</v>
@@ -22524,7 +22975,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>81</v>
@@ -22539,7 +22990,7 @@
         <v>109</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="M75" s="3">
         <v>5.0</v>
@@ -22553,13 +23004,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>51</v>
@@ -22582,7 +23033,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>81</v>
@@ -22639,7 +23090,7 @@
         <v>0.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AN77" s="3">
         <v>2.0</v>
@@ -22671,7 +23122,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>87</v>
@@ -22686,18 +23137,18 @@
         <v>88</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>51</v>
@@ -22714,7 +23165,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>87</v>
@@ -22771,7 +23222,7 @@
         <v>3.0</v>
       </c>
       <c r="AM80" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AN80" s="3">
         <v>0.0</v>
@@ -22803,7 +23254,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>92</v>
@@ -22823,13 +23274,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>59</v>
@@ -22838,7 +23289,7 @@
         <v>65</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M82" s="3">
         <v>5.0</v>
@@ -22846,7 +23297,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>92</v>
@@ -22906,7 +23357,7 @@
         <v>3.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN83" s="3">
         <v>0.0</v>
@@ -22938,7 +23389,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>49</v>
@@ -22958,7 +23409,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>49</v>
@@ -22981,13 +23432,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>59</v>
@@ -22996,18 +23447,18 @@
         <v>65</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>71</v>
@@ -23016,12 +23467,12 @@
         <v>84</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -23081,7 +23532,7 @@
         <v>2.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AN88" s="3">
         <v>0.0</v>
@@ -23113,7 +23564,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>63</v>
@@ -23133,7 +23584,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>63</v>
@@ -23156,7 +23607,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>63</v>
@@ -23219,7 +23670,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AN91" s="3">
         <v>0.0</v>
@@ -23251,7 +23702,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>69</v>
@@ -23271,7 +23722,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>69</v>
@@ -23294,7 +23745,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>69</v>
@@ -23354,7 +23805,7 @@
         <v>0.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN94" s="3">
         <v>0.0</v>
@@ -23386,7 +23837,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>78</v>
@@ -23406,7 +23857,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>78</v>
@@ -23429,7 +23880,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>78</v>
@@ -23489,7 +23940,7 @@
         <v>3.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -23521,13 +23972,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>51</v>
@@ -23541,7 +23992,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>81</v>
@@ -23561,7 +24012,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>81</v>
@@ -23581,13 +24032,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>65</v>
@@ -23610,7 +24061,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>81</v>
@@ -23619,7 +24070,7 @@
         <v>2.0</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>64</v>
@@ -23670,7 +24121,7 @@
         <v>0.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -23702,7 +24153,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>87</v>
@@ -23714,7 +24165,7 @@
         <v>59</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>73</v>
@@ -23722,7 +24173,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>87</v>
@@ -23731,24 +24182,24 @@
         <v>54</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>59</v>
@@ -23771,7 +24222,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>87</v>
@@ -23831,7 +24282,7 @@
         <v>1.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -24021,13 +24472,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -24041,13 +24492,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>59</v>
@@ -24061,7 +24512,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>78</v>
@@ -24081,13 +24532,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>59</v>
@@ -24110,7 +24561,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>78</v>
@@ -24139,7 +24590,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>78</v>
@@ -24193,7 +24644,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -24225,7 +24676,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>81</v>
@@ -24245,13 +24696,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>65</v>
@@ -24265,7 +24716,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>81</v>
@@ -24294,7 +24745,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>81</v>
@@ -24306,7 +24757,7 @@
         <v>64</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S11" s="3">
         <v>14680.0</v>
@@ -24354,7 +24805,7 @@
         <v>0.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN11" s="3">
         <v>1.0</v>
@@ -24386,7 +24837,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>87</v>
@@ -24406,13 +24857,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>65</v>
@@ -24421,18 +24872,18 @@
         <v>88</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>59</v>
@@ -24455,7 +24906,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>87</v>
@@ -24467,7 +24918,7 @@
         <v>64</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S15" s="3">
         <v>13889.0</v>
@@ -24515,7 +24966,7 @@
         <v>0.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN15" s="3">
         <v>1.0</v>
@@ -24547,13 +24998,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>51</v>
@@ -24567,13 +25018,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>59</v>
@@ -24596,13 +25047,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>55</v>
@@ -24616,7 +25067,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>92</v>
@@ -24670,7 +25121,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AN19" s="3">
         <v>1.0</v>
@@ -24702,7 +25153,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
@@ -24722,13 +25173,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>59</v>
@@ -24751,7 +25202,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>49</v>
@@ -24811,7 +25262,7 @@
         <v>0.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AN22" s="3">
         <v>1.0</v>
@@ -24843,7 +25294,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>63</v>
@@ -24863,13 +25314,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>59</v>
@@ -24892,7 +25343,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>63</v>
@@ -24952,7 +25403,7 @@
         <v>0.0</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AN25" s="3">
         <v>1.0</v>
@@ -24984,13 +25435,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>59</v>
@@ -25004,13 +25455,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>51</v>
@@ -25024,7 +25475,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>69</v>
@@ -25053,7 +25504,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>69</v>
@@ -25062,10 +25513,10 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S29" s="3">
         <v>9627.0</v>
@@ -25113,7 +25564,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -25145,13 +25596,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>51</v>
@@ -25165,7 +25616,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>78</v>
@@ -25194,13 +25645,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>51</v>
@@ -25214,7 +25665,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>78</v>
@@ -25223,10 +25674,10 @@
         <v>1.0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S33" s="3">
         <v>8650.0</v>
@@ -25274,7 +25725,7 @@
         <v>0.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -25306,7 +25757,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>81</v>
@@ -25326,13 +25777,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>65</v>
@@ -25341,12 +25792,12 @@
         <v>88</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>81</v>
@@ -25375,7 +25826,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>81</v>
@@ -25387,7 +25838,7 @@
         <v>64</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S37" s="3">
         <v>13913.0</v>
@@ -25435,7 +25886,7 @@
         <v>5.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AN37" s="3">
         <v>1.0</v>
@@ -25467,7 +25918,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>87</v>
@@ -25487,13 +25938,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>65</v>
@@ -25507,13 +25958,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>59</v>
@@ -25536,7 +25987,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>87</v>
@@ -25548,7 +25999,7 @@
         <v>64</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S41" s="3">
         <v>13277.0</v>
@@ -25596,7 +26047,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -25628,13 +26079,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>51</v>
@@ -25648,13 +26099,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>59</v>
@@ -25677,13 +26128,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>65</v>
@@ -25697,7 +26148,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>92</v>
@@ -25706,10 +26157,10 @@
         <v>0.0</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S45" s="3">
         <v>12722.0</v>
@@ -25757,7 +26208,7 @@
         <v>0.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AN45" s="3">
         <v>1.0</v>
@@ -25789,7 +26240,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>49</v>
@@ -25809,13 +26260,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>59</v>
@@ -25838,13 +26289,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>65</v>
@@ -25858,7 +26309,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
@@ -25918,7 +26369,7 @@
         <v>0.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AN49" s="3">
         <v>1.0</v>
@@ -25950,7 +26401,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>63</v>
@@ -25970,13 +26421,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>51</v>
@@ -25999,7 +26450,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>63</v>
@@ -26059,7 +26510,7 @@
         <v>0.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AN52" s="3">
         <v>1.0</v>
@@ -26091,13 +26542,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>65</v>
@@ -26111,7 +26562,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>69</v>
@@ -26144,7 +26595,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>69</v>
@@ -26154,7 +26605,7 @@
       <c r="E55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>51</v>
@@ -26168,7 +26619,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>69</v>
@@ -26226,7 +26677,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AN56" s="3">
         <v>1.0</v>
@@ -26258,13 +26709,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>51</v>
@@ -26278,13 +26729,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>59</v>
@@ -26307,19 +26758,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>51</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>59</v>
@@ -26327,7 +26778,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>78</v>
@@ -26336,10 +26787,10 @@
         <v>0.0</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S60" s="3">
         <v>18556.619999999995</v>
@@ -26387,7 +26838,7 @@
         <v>0.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AN60" s="3">
         <v>1.0</v>
@@ -26419,7 +26870,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>81</v>
@@ -26439,13 +26890,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>65</v>
@@ -26459,7 +26910,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>81</v>
@@ -26469,7 +26920,7 @@
       <c r="E63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>59</v>
@@ -26492,7 +26943,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>81</v>
@@ -26508,7 +26959,7 @@
         <v>64</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S64" s="3">
         <v>21825.50999999999</v>
@@ -26556,7 +27007,7 @@
         <v>0.0</v>
       </c>
       <c r="AM64" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN64" s="3">
         <v>1.0</v>
@@ -26588,7 +27039,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>87</v>
@@ -26608,13 +27059,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>65</v>
@@ -26628,13 +27079,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>59</v>
@@ -26657,7 +27108,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>87</v>
@@ -26711,7 +27162,7 @@
         <v>0.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -26743,13 +27194,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>51</v>
@@ -26763,13 +27214,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>59</v>
@@ -26792,7 +27243,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>92</v>
@@ -26846,7 +27297,7 @@
         <v>0.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AN71" s="3">
         <v>1.0</v>
@@ -26878,7 +27329,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -26898,13 +27349,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>59</v>
@@ -26927,7 +27378,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
@@ -26990,7 +27441,7 @@
         <v>0.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AN74" s="3">
         <v>1.0</v>
@@ -27022,7 +27473,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>63</v>
@@ -27042,13 +27493,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>59</v>
@@ -27057,7 +27508,7 @@
         <v>65</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M76" s="3">
         <v>2.0</v>
@@ -27071,13 +27522,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>65</v>
@@ -27100,7 +27551,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>63</v>
@@ -27160,7 +27611,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN78" s="3">
         <v>2.0</v>
@@ -27192,13 +27643,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>51</v>
@@ -27212,13 +27663,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>59</v>
@@ -27241,7 +27692,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>69</v>
@@ -27270,7 +27721,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
@@ -27279,10 +27730,10 @@
         <v>0.0</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S82" s="3">
         <v>12752.009999999998</v>
@@ -27327,7 +27778,7 @@
         <v>0.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN82" s="3">
         <v>2.0</v>
@@ -27359,13 +27810,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>65</v>
@@ -27379,7 +27830,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>78</v>
@@ -27408,13 +27859,13 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>51</v>
@@ -27431,7 +27882,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>78</v>
@@ -27440,7 +27891,7 @@
         <v>0.0</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S86" s="3">
         <v>17035.32</v>
@@ -27488,7 +27939,7 @@
         <v>0.0</v>
       </c>
       <c r="AM86" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN86" s="3">
         <v>1.0</v>
@@ -27520,7 +27971,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>81</v>
@@ -27540,13 +27991,13 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>65</v>
@@ -27560,7 +28011,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>81</v>
@@ -27589,7 +28040,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>81</v>
@@ -27601,7 +28052,7 @@
         <v>64</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S90" s="3">
         <v>25392.46</v>
@@ -27649,7 +28100,7 @@
         <v>0.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AN90" s="3">
         <v>1.0</v>
@@ -27681,7 +28132,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>87</v>
@@ -27701,13 +28152,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>65</v>
@@ -27721,13 +28172,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>59</v>
@@ -27750,7 +28201,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>87</v>
@@ -27762,7 +28213,7 @@
         <v>64</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S94" s="3">
         <v>23475.639999999996</v>
@@ -27842,13 +28293,13 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>51</v>
@@ -27862,19 +28313,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>59</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>217</v>
+        <v>121</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>53</v>
@@ -27891,7 +28342,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>92</v>
@@ -27900,10 +28351,10 @@
         <v>0.0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S97" s="3">
         <v>19985.18999999999</v>
@@ -27951,7 +28402,7 @@
         <v>0.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AN97" s="3">
         <v>1.0</v>
@@ -27983,7 +28434,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -28003,13 +28454,13 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>51</v>
@@ -28026,13 +28477,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>59</v>
@@ -28055,7 +28506,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
@@ -28112,7 +28563,7 @@
         <v>0.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AN101" s="3">
         <v>1.0</v>
@@ -28144,13 +28595,13 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>65</v>
@@ -28164,13 +28615,13 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>51</v>
@@ -28187,7 +28638,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>63</v>
@@ -28216,7 +28667,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>63</v>
@@ -28225,7 +28676,7 @@
         <v>0.0</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S105" s="3">
         <v>12356.0</v>
@@ -28273,7 +28724,7 @@
         <v>0.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AN105" s="3">
         <v>1.0</v>
@@ -28305,13 +28756,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>65</v>
@@ -28325,13 +28776,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>69</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>51</v>
@@ -28348,7 +28799,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>69</v>
@@ -28377,7 +28828,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>69</v>
@@ -28386,7 +28837,7 @@
         <v>0.0</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S109" s="3">
         <v>8748.0</v>
@@ -28434,7 +28885,7 @@
         <v>0.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AN109" s="3">
         <v>1.0</v>
@@ -28466,13 +28917,13 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>65</v>
@@ -28486,7 +28937,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>78</v>
@@ -28515,13 +28966,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>78</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>51</v>
@@ -28544,7 +28995,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>78</v>
@@ -28598,7 +29049,7 @@
         <v>0.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AN113" s="3">
         <v>2.0</v>
@@ -28630,13 +29081,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>65</v>
@@ -28650,7 +29101,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>81</v>
@@ -28670,13 +29121,13 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>59</v>
@@ -28699,13 +29150,13 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>51</v>
@@ -28722,7 +29173,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>81</v>
@@ -28731,7 +29182,7 @@
         <v>1.0</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S118" s="3">
         <v>22791.559999999998</v>
@@ -28779,7 +29230,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -28811,13 +29262,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>51</v>
@@ -28831,7 +29282,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>87</v>
@@ -28851,7 +29302,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>87</v>
@@ -28880,7 +29331,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>87</v>
@@ -28934,7 +29385,7 @@
         <v>0.0</v>
       </c>
       <c r="AM122" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AN122" s="3">
         <v>1.0</v>
